--- a/orders.xlsx
+++ b/orders.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mariavaulina/flights_creator/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE3DA82-E955-134A-92F6-FA388884531F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D36D0A9-FB43-5A41-B3FE-8F546E68DD5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="28800" windowHeight="17400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Рейсы" sheetId="1" r:id="rId1"/>
@@ -806,7 +806,7 @@
         <v>19</v>
       </c>
       <c r="H4" s="2">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="I4" s="2">
         <v>15000</v>
